--- a/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/ResumoThetaIC_3EM_MT_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/ResumoThetaIC_3EM_MT_S3.xlsx
@@ -395,22 +395,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>318.869</v>
+        <v>315.778</v>
       </c>
       <c r="C2" t="n">
-        <v>317.648</v>
+        <v>314.617</v>
       </c>
       <c r="D2" t="n">
-        <v>320.089</v>
+        <v>316.939</v>
       </c>
       <c r="E2" t="n">
-        <v>62.324</v>
+        <v>65.027</v>
       </c>
       <c r="F2" t="n">
-        <v>60.531</v>
+        <v>63.306</v>
       </c>
       <c r="G2" t="n">
-        <v>64.117</v>
+        <v>66.749</v>
       </c>
     </row>
     <row r="3">
@@ -418,22 +418,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>1.377</v>
+        <v>1.316</v>
       </c>
       <c r="C3" t="n">
-        <v>1.353</v>
+        <v>1.292</v>
       </c>
       <c r="D3" t="n">
-        <v>1.402</v>
+        <v>1.339</v>
       </c>
       <c r="E3" t="n">
-        <v>1.246</v>
+        <v>1.301</v>
       </c>
       <c r="F3" t="n">
-        <v>1.224</v>
+        <v>1.279</v>
       </c>
       <c r="G3" t="n">
-        <v>1.269</v>
+        <v>1.322</v>
       </c>
     </row>
   </sheetData>

--- a/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/ResumoThetaIC_3EM_MT_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/ResumoThetaIC_3EM_MT_S3.xlsx
@@ -395,22 +395,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>315.778</v>
+        <v>317.689</v>
       </c>
       <c r="C2" t="n">
-        <v>314.617</v>
+        <v>316.508</v>
       </c>
       <c r="D2" t="n">
-        <v>316.939</v>
+        <v>318.869</v>
       </c>
       <c r="E2" t="n">
-        <v>65.027</v>
+        <v>62.471</v>
       </c>
       <c r="F2" t="n">
-        <v>63.306</v>
+        <v>60.737</v>
       </c>
       <c r="G2" t="n">
-        <v>66.749</v>
+        <v>64.206</v>
       </c>
     </row>
     <row r="3">
@@ -418,22 +418,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>1.316</v>
+        <v>1.354</v>
       </c>
       <c r="C3" t="n">
-        <v>1.292</v>
+        <v>1.33</v>
       </c>
       <c r="D3" t="n">
-        <v>1.339</v>
+        <v>1.377</v>
       </c>
       <c r="E3" t="n">
-        <v>1.301</v>
+        <v>1.249</v>
       </c>
       <c r="F3" t="n">
-        <v>1.279</v>
+        <v>1.227</v>
       </c>
       <c r="G3" t="n">
-        <v>1.322</v>
+        <v>1.271</v>
       </c>
     </row>
   </sheetData>
